--- a/household_finance/templates/우리집_자산관리_템플릿.xlsx
+++ b/household_finance/templates/우리집_자산관리_템플릿.xlsx
@@ -11637,11 +11637,11 @@
           </c:spPr>
         </c:hiLowLines>
         <c:marker val="0"/>
-        <c:axId val="61076308"/>
-        <c:axId val="74543385"/>
+        <c:axId val="21482252"/>
+        <c:axId val="2381587"/>
       </c:lineChart>
       <c:catAx>
-        <c:axId val="61076308"/>
+        <c:axId val="21482252"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11673,7 +11673,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74543385"/>
+        <c:crossAx val="2381587"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -11681,7 +11681,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74543385"/>
+        <c:axId val="2381587"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -11723,7 +11723,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="61076308"/>
+        <c:crossAx val="21482252"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12236,11 +12236,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="85872045"/>
-        <c:axId val="30732915"/>
+        <c:axId val="28277442"/>
+        <c:axId val="7380337"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="85872045"/>
+        <c:axId val="28277442"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12272,7 +12272,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="30732915"/>
+        <c:crossAx val="7380337"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12280,7 +12280,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="30732915"/>
+        <c:axId val="7380337"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12322,7 +12322,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="85872045"/>
+        <c:crossAx val="28277442"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -12721,11 +12721,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="24455479"/>
-        <c:axId val="5888192"/>
+        <c:axId val="90765176"/>
+        <c:axId val="76765299"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="24455479"/>
+        <c:axId val="90765176"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -12757,7 +12757,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="5888192"/>
+        <c:crossAx val="76765299"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -12765,7 +12765,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="5888192"/>
+        <c:axId val="76765299"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -12807,7 +12807,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="24455479"/>
+        <c:crossAx val="90765176"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13098,11 +13098,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="58529319"/>
-        <c:axId val="412568"/>
+        <c:axId val="1438774"/>
+        <c:axId val="53705379"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="58529319"/>
+        <c:axId val="1438774"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13134,7 +13134,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="412568"/>
+        <c:crossAx val="53705379"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -13142,7 +13142,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="412568"/>
+        <c:axId val="53705379"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -13184,7 +13184,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="58529319"/>
+        <c:crossAx val="1438774"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -13606,7 +13606,7 @@
       </c>
       <c r="H4" s="6" t="n">
         <f aca="false">설정!$B$10</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>6</v>
@@ -13675,7 +13675,7 @@
       </c>
       <c r="E8" s="10"/>
       <c r="F8" s="10" t="str">
-        <f aca="false">"목표 "&amp;TEXT(설정!$B$29,"#,##0")&amp;" · 납입률 "&amp;TEXT(손익!M51,"0%")</f>
+        <f aca="false">"목표 "&amp;TEXT(설정!$B$29,"#,##0")&amp;IF(설정!$B$4="공동",""," · 납입률 "&amp;TEXT(손익!M51,"0%"))</f>
         <v>목표 2,200,000 · 납입률 0%</v>
       </c>
       <c r="G8" s="10"/>
@@ -23299,7 +23299,7 @@
       </c>
       <c r="B10" s="66" t="n">
         <f aca="true">TODAY()</f>
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="C10" s="64" t="s">
         <v>351</v>
@@ -29419,10 +29419,10 @@
         <v>0</v>
       </c>
       <c r="D4" s="50" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="E4" s="50" t="n">
-        <v>46671</v>
+        <v>46672</v>
       </c>
       <c r="F4" s="58"/>
       <c r="G4" s="58"/>
